--- a/outputs/daily/predictions_2026-06-29.xlsx
+++ b/outputs/daily/predictions_2026-06-29.xlsx
@@ -924,31 +924,31 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>1.432994702441934</v>
+        <v>1.426007895891515</v>
       </c>
       <c r="N2" t="n">
-        <v>1.067124973243461</v>
+        <v>1.06311177979388</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5470949040255653</v>
+        <v>0.5473606534741241</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2628047495770569</v>
+        <v>0.2627205453781711</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1901003463973779</v>
+        <v>0.1899188011477049</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4559345319918458</v>
+        <v>0.4508815819088509</v>
       </c>
       <c r="T2" t="n">
-        <v>1.643461675053509</v>
+        <v>1.630758390416382</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8565383249464911</v>
+        <v>0.8492416095836178</v>
       </c>
       <c r="V2" t="n">
         <v>0.4490351203406436</v>
@@ -966,25 +966,25 @@
         <v>0.520171282359564</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.4418602933459508</v>
+        <v>0.4409177469422212</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2896476091436642</v>
+        <v>0.2904662022529758</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.2684920975103853</v>
+        <v>0.2686160508048028</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.456217379061798</v>
+        <v>0.4533926947312659</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.543782620938202</v>
+        <v>0.5466073052687341</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.51203649754063</v>
+        <v>0.509917631944272</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.48796350245937</v>
+        <v>0.490082368055728</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
@@ -992,22 +992,22 @@
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
-        <v>1.432455</v>
+        <v>1.425635</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.070115</v>
+        <v>1.065505</v>
       </c>
       <c r="AO2" t="n">
-        <v>2.50257</v>
+        <v>2.49114</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.486465327065939</v>
+        <v>0.4863359902444302</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.267487751759613</v>
+        <v>0.2676587183573866</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.246046921174448</v>
+        <v>0.2460052913981831</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>0.486465327065939</v>
+        <v>0.4863359902444302</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.5138</v>
+        <v>0.5121</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.4862</v>
+        <v>0.4879</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>0.5138</v>
+        <v>0.5121</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
@@ -1043,10 +1043,10 @@
         <v>1</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.6422</v>
+        <v>0.6421</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.3578</v>
+        <v>0.3579</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="BE2" t="n">
-        <v>0.6422</v>
+        <v>0.6421</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.5821</v>
+        <v>0.582</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>5.260379683420678</v>
+        <v>5.265408132090479</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.246046921174448</v>
+        <v>0.2460052913981831</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.05594657477707005</v>
+        <v>0.05608649025047821</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.294300225314275</v>
+        <v>0.2953182618652812</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
@@ -1090,16 +1090,16 @@
         </is>
       </c>
       <c r="BO2" t="n">
-        <v>5.260379683420678</v>
+        <v>5.265408132090479</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.246046921174448</v>
+        <v>0.2460052913981831</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.05594657477707005</v>
+        <v>0.05608649025047821</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.294300225314275</v>
+        <v>0.2953182618652812</v>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="BT2" t="n">
-        <v>0.1380589406836399</v>
+        <v>0.1383830061727508</v>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="BV2" t="n">
-        <v>0.1050625230813936</v>
+        <v>0.1057541627279859</v>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="BX2" t="n">
-        <v>0.09462601911809365</v>
+        <v>0.09556328927126923</v>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="BZ2" t="n">
-        <v>0.08992624119290964</v>
+        <v>0.08969784520888495</v>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="CB2" t="n">
-        <v>0.08426964361970123</v>
+        <v>0.08437292005764048</v>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="CD2" t="n">
-        <v>0.07503368956801364</v>
+        <v>0.07563994852574631</v>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="CF2" t="n">
-        <v>0.06696642881047717</v>
+        <v>0.06687118362979122</v>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="CH2" t="n">
-        <v>0.04798126886343435</v>
+        <v>0.04767941793184684</v>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="CJ2" t="n">
-        <v>0.04673180486736007</v>
+        <v>0.04689397851334095</v>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="CL2" t="n">
-        <v>0.04295460907998506</v>
+        <v>0.04263661183744161</v>
       </c>
     </row>
     <row r="3">
@@ -1238,31 +1238,31 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>2.021786135589938</v>
+        <v>2.025874615494219</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8321798211816434</v>
+        <v>0.8335913412773617</v>
       </c>
       <c r="O3" t="b">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7044476440538116</v>
+        <v>0.7044163040533528</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1902442451882839</v>
+        <v>0.1902945498285736</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1053081107579046</v>
+        <v>0.1052891461180738</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5516989721333793</v>
+        <v>0.5530395535311398</v>
       </c>
       <c r="T3" t="n">
-        <v>2.139952525257482</v>
+        <v>2.147386125083449</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7500474747425178</v>
+        <v>0.7526138749165512</v>
       </c>
       <c r="V3" t="n">
         <v>0.6794640125002701</v>
@@ -1280,25 +1280,25 @@
         <v>0.4904008822833292</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.6412222998290671</v>
+        <v>0.6417247773981544</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2231966233667741</v>
+        <v>0.222803379766102</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1355810768041586</v>
+        <v>0.1354718428357436</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.5433060566671851</v>
+        <v>0.5445954588756171</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4566939433328149</v>
+        <v>0.4554045411243829</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4997899467556211</v>
+        <v>0.5006106390404254</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.5002100532443789</v>
+        <v>0.4993893609595746</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
@@ -1306,22 +1306,22 @@
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
-        <v>2.023035</v>
+        <v>2.027135</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.832025</v>
+        <v>0.83225</v>
       </c>
       <c r="AO3" t="n">
-        <v>2.85506</v>
+        <v>2.859385</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6798970369538859</v>
+        <v>0.6800101203459742</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.2016248663454255</v>
+        <v>0.2015466773013733</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.1184780967006886</v>
+        <v>0.1184432023526525</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1329,13 +1329,13 @@
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>0.6798970369538859</v>
+        <v>0.6800101203459742</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.4978</v>
+        <v>0.4984</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.5022</v>
+        <v>0.5016</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>0.5022</v>
+        <v>0.5016</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
@@ -1392,16 +1392,16 @@
         </is>
       </c>
       <c r="BO3" t="n">
-        <v>9.49594473590856</v>
+        <v>9.49765514176149</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.1184780967006886</v>
+        <v>0.1184432023526525</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.01316998594278397</v>
+        <v>0.01315405623457873</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.1250614586853693</v>
+        <v>0.1249326898313665</v>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
@@ -1409,23 +1409,23 @@
         </is>
       </c>
       <c r="BT3" t="n">
-        <v>0.1177559206479409</v>
+        <v>0.1175841825971672</v>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="BV3" t="n">
+        <v>0.1064418017857335</v>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
           <t>1-0</t>
         </is>
       </c>
-      <c r="BV3" t="n">
-        <v>0.1067932049278317</v>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
       <c r="BX3" t="n">
-        <v>0.1066319618966211</v>
+        <v>0.1064058615715029</v>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="BZ3" t="n">
-        <v>0.09799410098788322</v>
+        <v>0.09801715648417483</v>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="CB3" t="n">
-        <v>0.07935909591654527</v>
+        <v>0.0794036035690794</v>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="CD3" t="n">
-        <v>0.0673097106799451</v>
+        <v>0.06697641565063171</v>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="CF3" t="n">
-        <v>0.06604103824896752</v>
+        <v>0.0661901564014048</v>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="CH3" t="n">
-        <v>0.04077435671847628</v>
+        <v>0.04085312647091818</v>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="CJ3" t="n">
-        <v>0.04033498499244453</v>
+        <v>0.04033134741752211</v>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="CL3" t="n">
-        <v>0.04011177996425581</v>
+        <v>0.04021543621234104</v>
       </c>
     </row>
     <row r="4">
